--- a/testbed/example_data/metadata/DS_A-downloaded.xlsx
+++ b/testbed/example_data/metadata/DS_A-downloaded.xlsx
@@ -17,12 +17,11 @@
     <sheet name="ResearchDataFile" sheetId="8" state="visible" r:id="rId8"/>
     <sheet name="DataAccessPolicy" sheetId="9" state="visible" r:id="rId9"/>
     <sheet name="Individual" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="AnalysisMethodSupportingFile" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="AnalysisMethod" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet name="DataAccessCommittee" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet name="IndividualSupportingFile" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet name="Dataset" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet name="Sample" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet name="AnalysisMethod" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="DataAccessCommittee" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="IndividualSupportingFile" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="Dataset" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="Sample" sheetId="15" state="visible" r:id="rId15"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -679,112 +678,6 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H2"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="34" customWidth="1" min="1" max="1"/>
-    <col width="34" customWidth="1" min="2" max="2"/>
-    <col width="34" customWidth="1" min="3" max="3"/>
-    <col width="34" customWidth="1" min="4" max="4"/>
-    <col width="34" customWidth="1" min="5" max="5"/>
-    <col width="34" customWidth="1" min="6" max="6"/>
-    <col width="34" customWidth="1" min="7" max="7"/>
-    <col width="34" customWidth="1" min="8" max="8"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>alias</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>accession</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>analysis_method</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>name</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>dataset</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>included_in_submission</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>format</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>ega_accession</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>ANALYSIS_METHOD_SF_1</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>GHGAF03232138226677</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>GHGAZ24667350214243</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>analysis_method_1_parameters.txt</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>GHGAD77190331471604</t>
-        </is>
-      </c>
-      <c r="F2" t="b">
-        <v>1</v>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>TXT</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>EGAANALYSISMETHOD123456</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
   <dimension ref="A1:L2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -931,7 +824,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1006,7 +899,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1101,7 +994,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1251,7 +1144,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>

--- a/testbed/example_data/metadata/DS_A-downloaded.xlsx
+++ b/testbed/example_data/metadata/DS_A-downloaded.xlsx
@@ -1000,7 +1000,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H3"/>
+  <dimension ref="A1:H2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -1094,48 +1094,6 @@
       <c r="H2" t="inlineStr">
         <is>
           <t>EGADATASET000A</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>DS_B</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>GHGAD77190331471604</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>GHGAS51090952308378</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>GHGAP86954321096576</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>An interesting dataset B of complete example set</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>The complete-B dataset</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>And another Type</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>EGADATASET000B</t>
         </is>
       </c>
     </row>
@@ -2369,7 +2327,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H3"/>
+  <dimension ref="A1:H2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -2466,43 +2424,6 @@
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>STUDY_B</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>GHGAS51090952308378</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>EGASTUDY12346</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>A study that is the B study</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>The B Study</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>WHOLE_GENOME_SEQUENCING</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>Some Institute</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2514,7 +2435,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J10"/>
+  <dimension ref="A1:J4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -2725,294 +2646,6 @@
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>RESEARCH_DATA_FILE_4</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>GHGAF77721593457161</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>GHGAX39795256829841</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>SAMPLE_2_SPECIMEN_1_FILE_4.fastq.gz</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>LANE_126</t>
-        </is>
-      </c>
-      <c r="F5" t="n">
-        <v>1</v>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>GHGAD77190331471604</t>
-        </is>
-      </c>
-      <c r="H5" t="b">
-        <v>1</v>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>FASTQ</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>EGAFILE12349</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>RESEARCH_DATA_FILE_5</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>GHGAF91562421781007</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>GHGAX39795256829841</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>SAMPLE_2_SPECIMEN_1_FILE_5.fastq.gz</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>LANE_127</t>
-        </is>
-      </c>
-      <c r="F6" t="n">
-        <v>2</v>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>GHGAD77190331471604</t>
-        </is>
-      </c>
-      <c r="H6" t="b">
-        <v>1</v>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>FASTQ</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>EGAFILE12350</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>RESEARCH_DATA_FILE_6</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>GHGAF63374393909479</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>GHGAX39795256829841</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>SAMPLE_2_SPECIMEN_1_FILE_6.fastq.gz</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>LANE_128</t>
-        </is>
-      </c>
-      <c r="F7" t="n">
-        <v>3</v>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>GHGAD77190331471604</t>
-        </is>
-      </c>
-      <c r="H7" t="b">
-        <v>1</v>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>FASTQ</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>EGAFILE12351</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>RESEARCH_DATA_FILE_7</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>GHGAF24594710068561</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>GHGAX39795256829841</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>SAMPLE_2_SPECIMEN_1_FILE_7.fastq.gz</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>LANE_129</t>
-        </is>
-      </c>
-      <c r="F8" t="n">
-        <v>4</v>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>GHGAD77190331471604</t>
-        </is>
-      </c>
-      <c r="H8" t="b">
-        <v>1</v>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>FASTQ</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>EGAFILE12352</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>RESEARCH_DATA_FILE_8</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>GHGAF97000461197528</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>GHGAX39795256829841</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>SAMPLE_2_SPECIMEN_1_FILE_8.fastq.gz</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>LANE_130</t>
-        </is>
-      </c>
-      <c r="F9" t="n">
-        <v>5</v>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>GHGAD77190331471604</t>
-        </is>
-      </c>
-      <c r="H9" t="b">
-        <v>1</v>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>FASTQ</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>EGAFILE12353</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>RESEARCH_DATA_FILE_9</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>GHGAF58915171737891</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>GHGAX39795256829841</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>SAMPLE_2_SPECIMEN_1_FILE_9.fastq.gz</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>LANE_131</t>
-        </is>
-      </c>
-      <c r="F10" t="n">
-        <v>6</v>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>GHGAD77190331471604</t>
-        </is>
-      </c>
-      <c r="H10" t="b">
-        <v>1</v>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>FASTQ</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>EGAFILE12354</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3024,7 +2657,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L3"/>
+  <dimension ref="A1:L2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -3165,68 +2798,6 @@
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>DAP_2</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>GHGAP86954321096576</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>DUO:0000026</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>DAP 2</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>USER_SPECIFIC_RESTRICTION</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>http://some/other/policy</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>A Data Access Policy 2</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>This is a very strict DAP</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>NO_RESTRICTION</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>GHGAC82748725434213</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>DUO:0000004</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>EGADAP12346</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/testbed/example_data/metadata/DS_A-downloaded.xlsx
+++ b/testbed/example_data/metadata/DS_A-downloaded.xlsx
@@ -17,12 +17,11 @@
     <sheet name="ResearchDataFile" sheetId="8" state="visible" r:id="rId8"/>
     <sheet name="DataAccessPolicy" sheetId="9" state="visible" r:id="rId9"/>
     <sheet name="Individual" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="AnalysisMethodSupportingFile" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="AnalysisMethod" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet name="DataAccessCommittee" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet name="IndividualSupportingFile" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet name="Dataset" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet name="Sample" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet name="AnalysisMethod" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="DataAccessCommittee" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="IndividualSupportingFile" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="Dataset" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="Sample" sheetId="15" state="visible" r:id="rId15"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -679,112 +678,6 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H2"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="34" customWidth="1" min="1" max="1"/>
-    <col width="34" customWidth="1" min="2" max="2"/>
-    <col width="34" customWidth="1" min="3" max="3"/>
-    <col width="34" customWidth="1" min="4" max="4"/>
-    <col width="34" customWidth="1" min="5" max="5"/>
-    <col width="34" customWidth="1" min="6" max="6"/>
-    <col width="34" customWidth="1" min="7" max="7"/>
-    <col width="34" customWidth="1" min="8" max="8"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>alias</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>accession</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>analysis_method</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>name</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>dataset</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>included_in_submission</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>format</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>ega_accession</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>ANALYSIS_METHOD_SF_1</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>GHGAF03232138226677</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>GHGAZ24667350214243</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>analysis_method_1_parameters.txt</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>GHGAD77190331471604</t>
-        </is>
-      </c>
-      <c r="F2" t="b">
-        <v>1</v>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>TXT</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>EGAANALYSISMETHOD123456</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
   <dimension ref="A1:L2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -931,7 +824,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1006,7 +899,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1101,13 +994,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H3"/>
+  <dimension ref="A1:H2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -1204,54 +1097,12 @@
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>DS_B</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>GHGAD77190331471604</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>GHGAS51090952308378</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>GHGAP86954321096576</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>An interesting dataset B of complete example set</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>The complete-B dataset</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>And another Type</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>EGADATASET000B</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2476,7 +2327,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H3"/>
+  <dimension ref="A1:H2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -2573,43 +2424,6 @@
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>STUDY_B</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>GHGAS51090952308378</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>EGASTUDY12346</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>A study that is the B study</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>The B Study</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>WHOLE_GENOME_SEQUENCING</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>Some Institute</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2621,7 +2435,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J10"/>
+  <dimension ref="A1:J4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -2832,294 +2646,6 @@
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>RESEARCH_DATA_FILE_4</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>GHGAF77721593457161</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>GHGAX39795256829841</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>SAMPLE_2_SPECIMEN_1_FILE_4.fastq.gz</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>LANE_126</t>
-        </is>
-      </c>
-      <c r="F5" t="n">
-        <v>1</v>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>GHGAD77190331471604</t>
-        </is>
-      </c>
-      <c r="H5" t="b">
-        <v>1</v>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>FASTQ</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>EGAFILE12349</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>RESEARCH_DATA_FILE_5</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>GHGAF91562421781007</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>GHGAX39795256829841</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>SAMPLE_2_SPECIMEN_1_FILE_5.fastq.gz</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>LANE_127</t>
-        </is>
-      </c>
-      <c r="F6" t="n">
-        <v>2</v>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>GHGAD77190331471604</t>
-        </is>
-      </c>
-      <c r="H6" t="b">
-        <v>1</v>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>FASTQ</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>EGAFILE12350</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>RESEARCH_DATA_FILE_6</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>GHGAF63374393909479</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>GHGAX39795256829841</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>SAMPLE_2_SPECIMEN_1_FILE_6.fastq.gz</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>LANE_128</t>
-        </is>
-      </c>
-      <c r="F7" t="n">
-        <v>3</v>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>GHGAD77190331471604</t>
-        </is>
-      </c>
-      <c r="H7" t="b">
-        <v>1</v>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>FASTQ</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>EGAFILE12351</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>RESEARCH_DATA_FILE_7</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>GHGAF24594710068561</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>GHGAX39795256829841</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>SAMPLE_2_SPECIMEN_1_FILE_7.fastq.gz</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>LANE_129</t>
-        </is>
-      </c>
-      <c r="F8" t="n">
-        <v>4</v>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>GHGAD77190331471604</t>
-        </is>
-      </c>
-      <c r="H8" t="b">
-        <v>1</v>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>FASTQ</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>EGAFILE12352</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>RESEARCH_DATA_FILE_8</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>GHGAF97000461197528</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>GHGAX39795256829841</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>SAMPLE_2_SPECIMEN_1_FILE_8.fastq.gz</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>LANE_130</t>
-        </is>
-      </c>
-      <c r="F9" t="n">
-        <v>5</v>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>GHGAD77190331471604</t>
-        </is>
-      </c>
-      <c r="H9" t="b">
-        <v>1</v>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>FASTQ</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>EGAFILE12353</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>RESEARCH_DATA_FILE_9</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>GHGAF58915171737891</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>GHGAX39795256829841</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>SAMPLE_2_SPECIMEN_1_FILE_9.fastq.gz</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>LANE_131</t>
-        </is>
-      </c>
-      <c r="F10" t="n">
-        <v>6</v>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>GHGAD77190331471604</t>
-        </is>
-      </c>
-      <c r="H10" t="b">
-        <v>1</v>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>FASTQ</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>EGAFILE12354</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3131,7 +2657,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L3"/>
+  <dimension ref="A1:L2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -3272,68 +2798,6 @@
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>DAP_2</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>GHGAP86954321096576</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>DUO:0000026</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>DAP 2</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>USER_SPECIFIC_RESTRICTION</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>http://some/other/policy</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>A Data Access Policy 2</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>This is a very strict DAP</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>NO_RESTRICTION</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>GHGAC82748725434213</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>DUO:0000004</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>EGADAP12346</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
